--- a/Media/Template/Template-Target_tap_doan.xlsx
+++ b/Media/Template/Template-Target_tap_doan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DuyTu_E\SourceCode\ReportCenter\Report_Center\Media\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DuyTu_E\SourceCode\ReportCenter_V2\Report_Center_V2\Media\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2792513-5FCD-4AE6-ACB7-E15B43B54081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02005E7C-8CE9-4A84-B798-1659576D7754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4062CBE6-178B-418E-B143-C59D8D6D874A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4062CBE6-178B-418E-B143-C59D8D6D874A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
